--- a/FrontOffice/To_do.xlsx
+++ b/FrontOffice/To_do.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Liste des taches" sheetId="1" state="visible" r:id="rId3"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="45">
   <si>
     <t xml:space="preserve">Ligne</t>
   </si>
@@ -80,43 +80,61 @@
     <t xml:space="preserve">Liste articles</t>
   </si>
   <si>
-    <t xml:space="preserve">Recuperer liste article(avec categories) et chaque article</t>
+    <t xml:space="preserve">Recuperer liste article(avec categories)</t>
   </si>
   <si>
     <t xml:space="preserve">function.php/api.php</t>
   </si>
   <si>
+    <t xml:space="preserve">Metier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Article</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recuperer un article</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Afficher la liste des articles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">articles.php</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Afficher l'article</t>
+  </si>
+  <si>
+    <t xml:space="preserve">article.php</t>
+  </si>
+  <si>
     <t xml:space="preserve">Integration</t>
   </si>
   <si>
-    <t xml:space="preserve">Afficher la liste des articles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">articles.php</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Article</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Afficher l'article</t>
-  </si>
-  <si>
-    <t xml:space="preserve">article.php</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEO (liste articles et un article)</t>
+    <t xml:space="preserve">SEO (liste articles)</t>
   </si>
   <si>
     <t xml:space="preserve">Amelioration SEO avec implementation des meta , titres et url rewriting</t>
   </si>
   <si>
+    <t xml:space="preserve">(.htaccess)/articles.php</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEO (larticle)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(.htaccess)/article.php</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimisation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimisation du site : bundle.js, minimification css et js</t>
+  </si>
+  <si>
     <t xml:space="preserve">(.htaccess)</t>
   </si>
   <si>
-    <t xml:space="preserve">Optimisation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimisation du site : bundle.js, minimification css et js , activation gzip et cache du navigateur</t>
+    <t xml:space="preserve">Optimisation du site : activation gzip et cache du navigateur</t>
   </si>
   <si>
     <t xml:space="preserve">Test</t>
@@ -128,13 +146,13 @@
     <t xml:space="preserve">Toutes</t>
   </si>
   <si>
-    <t xml:space="preserve">Test &amp; correction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Effectuer l’evaluation sur lighthouse google(ajoute robots.txt) puis application des proposition d’amelioration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test &amp; Optimisation</t>
+    <t xml:space="preserve">Effectuer l’evaluation sur lighthouse google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Application des amelioration proposé par lighthouse google</t>
   </si>
   <si>
     <t xml:space="preserve">Somme - Estimation</t>
@@ -408,6 +426,31 @@
     <cellStyle name="Titre de la table dynamique" xfId="24"/>
     <cellStyle name="Valeur de la table dynamique" xfId="25"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC9DAF8"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -472,13 +515,13 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" recordCount="8" createdVersion="3">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" recordCount="14" createdVersion="3">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:K9" sheet="Liste des taches"/>
+    <worksheetSource ref="A1:K15" sheet="Liste des taches"/>
   </cacheSource>
   <cacheFields count="11">
     <cacheField name="Ligne" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="8" count="8">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="14" count="14">
         <n v="1"/>
         <n v="2"/>
         <n v="3"/>
@@ -487,17 +530,24 @@
         <n v="6"/>
         <n v="7"/>
         <n v="8"/>
+        <n v="9"/>
+        <n v="10"/>
+        <n v="11"/>
+        <n v="12"/>
+        <n v="13"/>
+        <n v="14"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Catégorie" numFmtId="0">
-      <sharedItems count="7">
+      <sharedItems count="8">
         <s v="Accueil"/>
         <s v="Article"/>
+        <s v="Correction"/>
         <s v="Liste articles"/>
         <s v="Optimisation"/>
-        <s v="SEO (liste articles et un article)"/>
+        <s v="SEO (larticle)"/>
+        <s v="SEO (liste articles)"/>
         <s v="Test"/>
-        <s v="Test &amp; correction"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Module" numFmtId="0">
@@ -506,20 +556,25 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Taches" numFmtId="0">
-      <sharedItems count="8">
+      <sharedItems count="11">
         <s v="Afficher l'article"/>
         <s v="Afficher la liste des articles"/>
         <s v="Amelioration SEO avec implementation des meta , titres et url rewriting"/>
+        <s v="Application des amelioration proposé par lighthouse google"/>
         <s v="Creation d’une page index.php comme accuiel"/>
-        <s v="Effectuer l’evaluation sur lighthouse google(ajoute robots.txt) puis application des proposition d’amelioration"/>
+        <s v="Effectuer l’evaluation sur lighthouse google"/>
         <s v="Effectuer un test complet :afficher liste des articles,afficher article,tester les images,tester URL seo"/>
-        <s v="Optimisation du site : bundle.js, minimification css , activation gzip et cache du navigateur"/>
-        <s v="Recuperer liste article(avec categories) et chaque article"/>
+        <s v="Optimisation du site : activation gzip et cache du navigateur"/>
+        <s v="Optimisation du site : bundle.js, minimification css et js"/>
+        <s v="Recuperer liste article(avec categories)"/>
+        <s v="Recuperer un article"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Pages" numFmtId="0">
-      <sharedItems count="6">
+      <sharedItems count="8">
         <s v="(.htaccess)"/>
+        <s v="(.htaccess)/article.php"/>
+        <s v="(.htaccess)/articles.php"/>
         <s v="article.php"/>
         <s v="articles.php"/>
         <s v="function.php/api.php"/>
@@ -531,9 +586,9 @@
       <sharedItems count="5">
         <s v="Affichage"/>
         <s v="Integration"/>
+        <s v="Metier"/>
         <s v="Optimisation"/>
         <s v="Test"/>
-        <s v="Test &amp; Optimisation"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Qui" numFmtId="0">
@@ -542,30 +597,29 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Estimation" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="10" maxValue="30" count="5">
-        <n v="10"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="15" maxValue="30" count="3">
         <n v="15"/>
         <n v="20"/>
-        <n v="25"/>
         <n v="30"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Temps passé" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="10" maxValue="30" count="5">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="10" maxValue="30" count="4">
         <n v="10"/>
         <n v="15"/>
         <n v="20"/>
-        <n v="25"/>
         <n v="30"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Reste à faire" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="0" count="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="5" count="2">
         <n v="0"/>
+        <n v="5"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Avancement" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="1" count="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.666666666666667" maxValue="1" count="2">
+        <n v="0.666666666666667"/>
         <n v="1"/>
       </sharedItems>
     </cacheField>
@@ -574,110 +628,188 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="8">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="14">
   <r>
     <x v="0"/>
     <x v="0"/>
     <x v="0"/>
-    <x v="3"/>
     <x v="4"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
+    <x v="6"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
   </r>
   <r>
     <x v="1"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="9"/>
+    <x v="5"/>
     <x v="2"/>
     <x v="0"/>
-    <x v="7"/>
-    <x v="3"/>
-    <x v="1"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-    <x v="0"/>
-    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
   </r>
   <r>
     <x v="2"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="10"/>
+    <x v="5"/>
     <x v="2"/>
     <x v="0"/>
-    <x v="1"/>
-    <x v="2"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="1"/>
-    <x v="1"/>
-    <x v="0"/>
-    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
   </r>
   <r>
     <x v="3"/>
-    <x v="1"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="1"/>
-    <x v="0"/>
-    <x v="0"/>
     <x v="3"/>
-    <x v="3"/>
-    <x v="0"/>
-    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
   </r>
   <r>
     <x v="4"/>
-    <x v="4"/>
-    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
     <x v="2"/>
     <x v="0"/>
     <x v="1"/>
-    <x v="0"/>
-    <x v="4"/>
-    <x v="4"/>
-    <x v="0"/>
-    <x v="0"/>
   </r>
   <r>
     <x v="5"/>
     <x v="3"/>
     <x v="0"/>
-    <x v="6"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-    <x v="1"/>
-    <x v="1"/>
-    <x v="0"/>
-    <x v="0"/>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
   </r>
   <r>
     <x v="6"/>
-    <x v="5"/>
-    <x v="0"/>
-    <x v="5"/>
-    <x v="5"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
     <x v="3"/>
-    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
     <x v="2"/>
-    <x v="2"/>
-    <x v="0"/>
-    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
   </r>
   <r>
     <x v="7"/>
     <x v="6"/>
     <x v="0"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="9"/>
     <x v="4"/>
+    <x v="0"/>
+    <x v="8"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="7"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="7"/>
+    <x v="0"/>
+    <x v="6"/>
+    <x v="7"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <x v="7"/>
+    <x v="0"/>
     <x v="5"/>
+    <x v="7"/>
     <x v="4"/>
     <x v="0"/>
-    <x v="4"/>
-    <x v="4"/>
-    <x v="0"/>
-    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="7"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="1"/>
   </r>
 </pivotCacheRecords>
 </file>
@@ -909,7 +1041,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="83.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="75.18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="19.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.67"/>
   </cols>
@@ -972,10 +1104,10 @@
         <v>16</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J2" s="4" t="n">
         <f aca="false">H2-I2</f>
@@ -1009,10 +1141,10 @@
         <v>16</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J3" s="4" t="n">
         <f aca="false">H3-I3</f>
@@ -1028,19 +1160,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>16</v>
@@ -1065,16 +1197,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>25</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>15</v>
@@ -1083,10 +1215,10 @@
         <v>16</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="J5" s="4" t="n">
         <f aca="false">H5-I5</f>
@@ -1102,28 +1234,28 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J6" s="4" t="n">
         <f aca="false">H6-I6</f>
@@ -1139,19 +1271,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>16</v>
@@ -1176,19 +1308,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>16</v>
@@ -1213,28 +1345,28 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J9" s="4" t="n">
         <f aca="false">H9-I9</f>
@@ -1245,12 +1377,228 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <f aca="false">H10-I10</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="7" t="n">
+        <f aca="false">I10/(I10+J10)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <f aca="false">H11-I11</f>
+        <v>5</v>
+      </c>
+      <c r="K11" s="7" t="n">
+        <f aca="false">I11/(I11+J11)</f>
+        <v>0.666666666666667</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <f aca="false">H12-I12</f>
+        <v>0</v>
+      </c>
+      <c r="K12" s="7" t="n">
+        <f aca="false">I12/(I12+J12)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <f aca="false">H13-I13</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="7" t="n">
+        <f aca="false">I13/(I13+J13)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <f aca="false">H14-I14</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="7" t="n">
+        <f aca="false">I14/(I14+J14)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <f aca="false">H15-I15</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="7" t="n">
+        <f aca="false">I15/(I15+J15)</f>
+        <v>1</v>
+      </c>
+    </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2224,11 +2572,11 @@
     <row r="986" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="987" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="988" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048561" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="989" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="990" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="991" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="992" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="993" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2259,8 +2607,8 @@
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17.85"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2268,7 +2616,7 @@
         <v>6</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2276,15 +2624,15 @@
         <v>16</v>
       </c>
       <c r="B2" s="11" t="n">
-        <v>165</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B3" s="13" t="n">
-        <v>165</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
